--- a/graphic.xlsx
+++ b/graphic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vaaba\Desktop\MyBot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F22F75-84A9-4606-89AA-5BE08648E090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C97FF86-C31D-4DFB-B71C-704A23C2E92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -525,7 +525,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -569,7 +569,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -613,7 +613,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -657,7 +657,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -801,7 +801,7 @@
         <v>7</v>
       </c>
       <c r="C33" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -849,7 +849,7 @@
         <v>7</v>
       </c>
       <c r="C37" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -897,7 +897,7 @@
         <v>7</v>
       </c>
       <c r="C41" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1137,7 +1137,7 @@
         <v>7</v>
       </c>
       <c r="C61" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1185,7 +1185,7 @@
         <v>7</v>
       </c>
       <c r="C65" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1233,7 +1233,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1281,7 +1281,7 @@
         <v>7</v>
       </c>
       <c r="C73" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1329,7 +1329,7 @@
         <v>7</v>
       </c>
       <c r="C77" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <f t="shared" ref="A87:A150" si="1">A83+1</f>
+        <f t="shared" ref="A87:A121" si="1">A83+1</f>
         <v>46195</v>
       </c>
       <c r="B87" t="s">
@@ -1473,7 +1473,7 @@
         <v>7</v>
       </c>
       <c r="C89" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -1521,7 +1521,7 @@
         <v>7</v>
       </c>
       <c r="C93" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -1569,7 +1569,7 @@
         <v>7</v>
       </c>
       <c r="C97" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -1617,7 +1617,7 @@
         <v>7</v>
       </c>
       <c r="C101" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -1665,7 +1665,7 @@
         <v>7</v>
       </c>
       <c r="C105" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -1809,7 +1809,7 @@
         <v>7</v>
       </c>
       <c r="C117" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -1857,7 +1857,7 @@
         <v>7</v>
       </c>
       <c r="C121" s="2">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">

--- a/graphic.xlsx
+++ b/graphic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vaaba\Desktop\MyBot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C97FF86-C31D-4DFB-B71C-704A23C2E92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B097817-D1FD-4326-9673-B6C5105433F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="10">
   <si>
     <t>A (День)</t>
   </si>
@@ -758,7 +758,6 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <f t="shared" si="0"/>
         <v>46181</v>
       </c>
       <c r="B30" t="s">
@@ -770,7 +769,6 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <f t="shared" si="0"/>
         <v>46181</v>
       </c>
       <c r="B31" t="s">
@@ -782,19 +780,17 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <f t="shared" si="0"/>
         <v>46181</v>
       </c>
       <c r="B32" t="s">
         <v>5</v>
       </c>
-      <c r="C32" t="s">
-        <v>6</v>
+      <c r="C32" s="2">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <f t="shared" si="0"/>
         <v>46181</v>
       </c>
       <c r="B33" t="s">
@@ -806,7 +802,6 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <f t="shared" si="0"/>
         <v>46182</v>
       </c>
       <c r="B34" t="s">
@@ -818,7 +813,6 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <f t="shared" si="0"/>
         <v>46182</v>
       </c>
       <c r="B35" t="s">
@@ -830,7 +824,6 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <f t="shared" si="0"/>
         <v>46182</v>
       </c>
       <c r="B36" t="s">
@@ -842,7 +835,6 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <f t="shared" si="0"/>
         <v>46182</v>
       </c>
       <c r="B37" t="s">
@@ -854,7 +846,6 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <f t="shared" si="0"/>
         <v>46183</v>
       </c>
       <c r="B38" t="s">
@@ -866,7 +857,6 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <f t="shared" si="0"/>
         <v>46183</v>
       </c>
       <c r="B39" t="s">
@@ -878,7 +868,6 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <f t="shared" si="0"/>
         <v>46183</v>
       </c>
       <c r="B40" t="s">
@@ -890,7 +879,6 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <f t="shared" si="0"/>
         <v>46183</v>
       </c>
       <c r="B41" t="s">
@@ -902,7 +890,6 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <f t="shared" si="0"/>
         <v>46184</v>
       </c>
       <c r="B42" t="s">
@@ -914,7 +901,6 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <f t="shared" si="0"/>
         <v>46184</v>
       </c>
       <c r="B43" t="s">
@@ -926,7 +912,6 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <f t="shared" si="0"/>
         <v>46184</v>
       </c>
       <c r="B44" t="s">
@@ -938,7 +923,6 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <f t="shared" si="0"/>
         <v>46184</v>
       </c>
       <c r="B45" t="s">
@@ -950,7 +934,6 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="B46" t="s">
@@ -962,7 +945,6 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="B47" t="s">
@@ -974,7 +956,6 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="B48" t="s">
@@ -986,7 +967,6 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <f t="shared" si="0"/>
         <v>46185</v>
       </c>
       <c r="B49" t="s">
@@ -998,7 +978,6 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <f t="shared" si="0"/>
         <v>46186</v>
       </c>
       <c r="B50" t="s">
@@ -1010,7 +989,6 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <f t="shared" si="0"/>
         <v>46186</v>
       </c>
       <c r="B51" t="s">
@@ -1022,7 +1000,6 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <f t="shared" si="0"/>
         <v>46186</v>
       </c>
       <c r="B52" t="s">
@@ -1034,7 +1011,6 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <f t="shared" si="0"/>
         <v>46186</v>
       </c>
       <c r="B53" t="s">
@@ -1046,7 +1022,6 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <f t="shared" si="0"/>
         <v>46187</v>
       </c>
       <c r="B54" t="s">
@@ -1058,7 +1033,6 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <f t="shared" si="0"/>
         <v>46187</v>
       </c>
       <c r="B55" t="s">
@@ -1070,7 +1044,6 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <f t="shared" si="0"/>
         <v>46187</v>
       </c>
       <c r="B56" t="s">
@@ -1082,7 +1055,6 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <f t="shared" si="0"/>
         <v>46187</v>
       </c>
       <c r="B57" t="s">
@@ -1094,7 +1066,6 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <f t="shared" si="0"/>
         <v>46188</v>
       </c>
       <c r="B58" t="s">
@@ -1106,7 +1077,6 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <f t="shared" si="0"/>
         <v>46188</v>
       </c>
       <c r="B59" t="s">
@@ -1118,7 +1088,6 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <f t="shared" si="0"/>
         <v>46188</v>
       </c>
       <c r="B60" t="s">
@@ -1130,7 +1099,6 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <f t="shared" si="0"/>
         <v>46188</v>
       </c>
       <c r="B61" t="s">
@@ -1142,7 +1110,6 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <f t="shared" si="0"/>
         <v>46189</v>
       </c>
       <c r="B62" t="s">
@@ -1154,7 +1121,6 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <f t="shared" si="0"/>
         <v>46189</v>
       </c>
       <c r="B63" t="s">
@@ -1166,7 +1132,6 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <f t="shared" si="0"/>
         <v>46189</v>
       </c>
       <c r="B64" t="s">
@@ -1178,7 +1143,6 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <f t="shared" si="0"/>
         <v>46189</v>
       </c>
       <c r="B65" t="s">
@@ -1190,7 +1154,6 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <f t="shared" si="0"/>
         <v>46190</v>
       </c>
       <c r="B66" t="s">
@@ -1202,7 +1165,6 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <f t="shared" si="0"/>
         <v>46190</v>
       </c>
       <c r="B67" t="s">
@@ -1214,7 +1176,6 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <f t="shared" si="0"/>
         <v>46190</v>
       </c>
       <c r="B68" t="s">
@@ -1226,7 +1187,6 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <f t="shared" si="0"/>
         <v>46190</v>
       </c>
       <c r="B69" t="s">
@@ -1238,7 +1198,6 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <f t="shared" si="0"/>
         <v>46191</v>
       </c>
       <c r="B70" t="s">
@@ -1250,7 +1209,6 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <f t="shared" si="0"/>
         <v>46191</v>
       </c>
       <c r="B71" t="s">
@@ -1262,7 +1220,6 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <f t="shared" si="0"/>
         <v>46191</v>
       </c>
       <c r="B72" t="s">
@@ -1274,7 +1231,6 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <f t="shared" si="0"/>
         <v>46191</v>
       </c>
       <c r="B73" t="s">
@@ -1286,7 +1242,6 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <f t="shared" si="0"/>
         <v>46192</v>
       </c>
       <c r="B74" t="s">
@@ -1298,7 +1253,6 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <f t="shared" si="0"/>
         <v>46192</v>
       </c>
       <c r="B75" t="s">
@@ -1310,7 +1264,6 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <f t="shared" si="0"/>
         <v>46192</v>
       </c>
       <c r="B76" t="s">
@@ -1322,7 +1275,6 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <f t="shared" si="0"/>
         <v>46192</v>
       </c>
       <c r="B77" t="s">
@@ -1334,7 +1286,6 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <f t="shared" si="0"/>
         <v>46193</v>
       </c>
       <c r="B78" t="s">
@@ -1346,7 +1297,6 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <f t="shared" si="0"/>
         <v>46193</v>
       </c>
       <c r="B79" t="s">
@@ -1358,7 +1308,6 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <f t="shared" si="0"/>
         <v>46193</v>
       </c>
       <c r="B80" t="s">
@@ -1370,7 +1319,6 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <f t="shared" si="0"/>
         <v>46193</v>
       </c>
       <c r="B81" t="s">
@@ -1382,7 +1330,6 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <f t="shared" si="0"/>
         <v>46194</v>
       </c>
       <c r="B82" t="s">
@@ -1394,7 +1341,6 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <f t="shared" si="0"/>
         <v>46194</v>
       </c>
       <c r="B83" t="s">
@@ -1406,7 +1352,6 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <f t="shared" si="0"/>
         <v>46194</v>
       </c>
       <c r="B84" t="s">
@@ -1418,7 +1363,6 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <f t="shared" si="0"/>
         <v>46194</v>
       </c>
       <c r="B85" t="s">
@@ -1430,7 +1374,6 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <f t="shared" si="0"/>
         <v>46195</v>
       </c>
       <c r="B86" t="s">
@@ -1442,7 +1385,6 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <f t="shared" ref="A87:A121" si="1">A83+1</f>
         <v>46195</v>
       </c>
       <c r="B87" t="s">
@@ -1454,7 +1396,6 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <f t="shared" si="1"/>
         <v>46195</v>
       </c>
       <c r="B88" t="s">
@@ -1466,7 +1407,6 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <f t="shared" si="1"/>
         <v>46195</v>
       </c>
       <c r="B89" t="s">
@@ -1478,7 +1418,6 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <f t="shared" si="1"/>
         <v>46196</v>
       </c>
       <c r="B90" t="s">
@@ -1490,7 +1429,6 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <f t="shared" si="1"/>
         <v>46196</v>
       </c>
       <c r="B91" t="s">
@@ -1502,7 +1440,6 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <f t="shared" si="1"/>
         <v>46196</v>
       </c>
       <c r="B92" t="s">
@@ -1514,7 +1451,6 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <f t="shared" si="1"/>
         <v>46196</v>
       </c>
       <c r="B93" t="s">
@@ -1526,7 +1462,6 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <f t="shared" si="1"/>
         <v>46197</v>
       </c>
       <c r="B94" t="s">
@@ -1538,7 +1473,6 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <f t="shared" si="1"/>
         <v>46197</v>
       </c>
       <c r="B95" t="s">
@@ -1550,7 +1484,6 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <f t="shared" si="1"/>
         <v>46197</v>
       </c>
       <c r="B96" t="s">
@@ -1562,7 +1495,6 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <f t="shared" si="1"/>
         <v>46197</v>
       </c>
       <c r="B97" t="s">
@@ -1574,7 +1506,6 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <f t="shared" si="1"/>
         <v>46198</v>
       </c>
       <c r="B98" t="s">
@@ -1586,7 +1517,6 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <f t="shared" si="1"/>
         <v>46198</v>
       </c>
       <c r="B99" t="s">
@@ -1598,7 +1528,6 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <f t="shared" si="1"/>
         <v>46198</v>
       </c>
       <c r="B100" t="s">
@@ -1610,7 +1539,6 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <f t="shared" si="1"/>
         <v>46198</v>
       </c>
       <c r="B101" t="s">
@@ -1622,7 +1550,6 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <f t="shared" si="1"/>
         <v>46199</v>
       </c>
       <c r="B102" t="s">
@@ -1634,7 +1561,6 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <f t="shared" si="1"/>
         <v>46199</v>
       </c>
       <c r="B103" t="s">
@@ -1646,7 +1572,6 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <f t="shared" si="1"/>
         <v>46199</v>
       </c>
       <c r="B104" t="s">
@@ -1658,7 +1583,6 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <f t="shared" si="1"/>
         <v>46199</v>
       </c>
       <c r="B105" t="s">
@@ -1670,7 +1594,6 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <f t="shared" si="1"/>
         <v>46200</v>
       </c>
       <c r="B106" t="s">
@@ -1682,7 +1605,6 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <f t="shared" si="1"/>
         <v>46200</v>
       </c>
       <c r="B107" t="s">
@@ -1694,7 +1616,6 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <f t="shared" si="1"/>
         <v>46200</v>
       </c>
       <c r="B108" t="s">
@@ -1706,7 +1627,6 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <f t="shared" si="1"/>
         <v>46200</v>
       </c>
       <c r="B109" t="s">
@@ -1718,7 +1638,6 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <f t="shared" si="1"/>
         <v>46201</v>
       </c>
       <c r="B110" t="s">
@@ -1730,7 +1649,6 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <f t="shared" si="1"/>
         <v>46201</v>
       </c>
       <c r="B111" t="s">
@@ -1742,7 +1660,6 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <f t="shared" si="1"/>
         <v>46201</v>
       </c>
       <c r="B112" t="s">
@@ -1754,7 +1671,6 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <f t="shared" si="1"/>
         <v>46201</v>
       </c>
       <c r="B113" t="s">
@@ -1766,7 +1682,6 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <f t="shared" si="1"/>
         <v>46202</v>
       </c>
       <c r="B114" t="s">
@@ -1778,7 +1693,6 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <f t="shared" si="1"/>
         <v>46202</v>
       </c>
       <c r="B115" t="s">
@@ -1790,7 +1704,6 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <f t="shared" si="1"/>
         <v>46202</v>
       </c>
       <c r="B116" t="s">
@@ -1802,7 +1715,6 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <f t="shared" si="1"/>
         <v>46202</v>
       </c>
       <c r="B117" t="s">
@@ -1814,7 +1726,6 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <f t="shared" si="1"/>
         <v>46203</v>
       </c>
       <c r="B118" t="s">
@@ -1826,7 +1737,6 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <f t="shared" si="1"/>
         <v>46203</v>
       </c>
       <c r="B119" t="s">
@@ -1838,7 +1748,6 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <f t="shared" si="1"/>
         <v>46203</v>
       </c>
       <c r="B120" t="s">
@@ -1850,7 +1759,6 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <f t="shared" si="1"/>
         <v>46203</v>
       </c>
       <c r="B121" t="s">
